--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.50782268842248</v>
+        <v>4.957521186868653</v>
       </c>
       <c r="D2" t="n">
-        <v>30.09375893294525</v>
+        <v>4.890235826603603</v>
       </c>
       <c r="E2" t="n">
-        <v>14.59720846564207</v>
+        <v>2.372046375666837</v>
       </c>
       <c r="F2" t="n">
-        <v>14.14292197792377</v>
+        <v>2.298224821412613</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.31340575713833</v>
+        <v>0.2134284355349786</v>
       </c>
       <c r="D3" t="n">
-        <v>1.807914977097705</v>
+        <v>0.2937861837783771</v>
       </c>
       <c r="E3" t="n">
-        <v>14.59720846564207</v>
+        <v>2.372046375666837</v>
       </c>
       <c r="F3" t="n">
-        <v>14.14292197792377</v>
+        <v>2.298224821412613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
